--- a/public/downloads/underwriting-demo/sample-rent-roll-analysis.xlsx
+++ b/public/downloads/underwriting-demo/sample-rent-roll-analysis.xlsx
@@ -9,8 +9,7 @@
   <sheets>
     <sheet name="Rent Roll" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Unit Mix Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Lease Trade-Out" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Audit Trail" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Audit Trail" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9367,222 +9366,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="25" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Lease trade-out</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Fixture Park — as of 2026-06-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Gross and effective are both stated: concessions are what separate them, and quoting one as the other is how a trade-out number becomes wrong.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="n"/>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="n"/>
-      <c r="H4" s="3" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Cohort</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Leases</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Prior rent</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>New rent (gross)</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Gross change ($)</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Gross change (%)</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>New rent (effective)</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Effective change ($)</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>Effective change (%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="n">
-        <v>46</v>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>1706</v>
-      </c>
-      <c r="D6" s="7" t="n">
-        <v>1812</v>
-      </c>
-      <c r="E6" s="7">
-        <f>IFERROR(D6-C6,"")</f>
-        <v/>
-      </c>
-      <c r="F6" s="19">
-        <f>IFERROR((D6-C6)/C6,"")</f>
-        <v/>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>1774</v>
-      </c>
-      <c r="H6" s="7">
-        <f>IFERROR(G6-C6,"")</f>
-        <v/>
-      </c>
-      <c r="I6" s="19">
-        <f>IFERROR((G6-C6)/C6,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Renewal</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="n">
-        <v>88</v>
-      </c>
-      <c r="C7" s="7" t="n">
-        <v>1698</v>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>1745</v>
-      </c>
-      <c r="E7" s="7">
-        <f>IFERROR(D7-C7,"")</f>
-        <v/>
-      </c>
-      <c r="F7" s="19">
-        <f>IFERROR((D7-C7)/C7,"")</f>
-        <v/>
-      </c>
-      <c r="G7" s="7" t="n">
-        <v>1745</v>
-      </c>
-      <c r="H7" s="7">
-        <f>IFERROR(G7-C7,"")</f>
-        <v/>
-      </c>
-      <c r="I7" s="19">
-        <f>IFERROR((G7-C7)/C7,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>First generation</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="C8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>1836</v>
-      </c>
-      <c r="E8" s="7">
-        <f>IFERROR(D8-C8,"")</f>
-        <v/>
-      </c>
-      <c r="F8" s="19">
-        <f>IFERROR((D8-C8)/C8,"")</f>
-        <v/>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>1790</v>
-      </c>
-      <c r="H8" s="7">
-        <f>IFERROR(G8-C8,"")</f>
-        <v/>
-      </c>
-      <c r="I8" s="19">
-        <f>IFERROR((G8-C8)/C8,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>A first-generation lease has no prior rent, so its percentage change is undefined and reads blank rather than as a number divided by zero.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -9612,7 +9395,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>The rent roll, unit mix and trade-out. Every value below names the document it came from and where in it. A derived value names the values it was built from — one that could not would not have passed validation.</t>
+          <t>The rent roll and unit mix. Every value below names the document it came from and where in it. A derived value names the values it was built from — one that could not would not have passed validation.</t>
         </is>
       </c>
     </row>
@@ -9932,12 +9715,12 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>3 entries</t>
+          <t>0 entries</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Synthetic lease trade-out report</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -9953,7 +9736,7 @@
       <c r="F16" s="10" t="n"/>
       <c r="G16" s="23" t="inlineStr">
         <is>
-          <t>Cohort averages.</t>
+          <t>The internal pipeline reads a lease trade-out report (new versus renewal rents); the demo does not ask for one.</t>
         </is>
       </c>
     </row>

--- a/public/downloads/underwriting-demo/sample-rent-roll-analysis.xlsx
+++ b/public/downloads/underwriting-demo/sample-rent-roll-analysis.xlsx
@@ -16481,7 +16481,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Not asked for by the upload demo</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -16497,7 +16497,7 @@
       <c r="F16" s="10" t="n"/>
       <c r="G16" s="22" t="inlineStr">
         <is>
-          <t>The upload demo does not ask for a lease trade-out report, so there is no basis for a new-versus-renewal block.</t>
+          <t>The internal pipeline reads a lease trade-out report (new versus renewal rents); the demo does not ask for one.</t>
         </is>
       </c>
     </row>

--- a/public/downloads/underwriting-demo/sample-rent-roll-analysis.xlsx
+++ b/public/downloads/underwriting-demo/sample-rent-roll-analysis.xlsx
@@ -828,7 +828,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Southern Avenue Sample — as of 2026-08-31</t>
+          <t>505 West — as of 2026-08-31</t>
         </is>
       </c>
     </row>
@@ -15445,7 +15445,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Southern Avenue Sample — as of 2026-08-31</t>
+          <t>505 West — as of 2026-08-31</t>
         </is>
       </c>
     </row>
@@ -16145,7 +16145,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Southern Avenue Sample — as of 2026-08-31</t>
+          <t>505 West — as of 2026-08-31</t>
         </is>
       </c>
     </row>

--- a/public/downloads/underwriting-demo/sample-rent-roll-analysis.xlsx
+++ b/public/downloads/underwriting-demo/sample-rent-roll-analysis.xlsx
@@ -828,7 +828,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>505 West — as of 2026-08-31</t>
+          <t>Sample Mesa Apt — as of 2026-08-31</t>
         </is>
       </c>
     </row>
@@ -15445,7 +15445,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>505 West — as of 2026-08-31</t>
+          <t>Sample Mesa Apt — as of 2026-08-31</t>
         </is>
       </c>
     </row>
@@ -16145,7 +16145,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>505 West — as of 2026-08-31</t>
+          <t>Sample Mesa Apt — as of 2026-08-31</t>
         </is>
       </c>
     </row>

--- a/public/downloads/underwriting-demo/sample-rent-roll-analysis.xlsx
+++ b/public/downloads/underwriting-demo/sample-rent-roll-analysis.xlsx
@@ -331,7 +331,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>In-place vs new-lease vs market rent for model</a:t>
+              <a:t>In-place vs new move-in vs market rent for model</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -370,30 +370,6 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Unit Mix Summary'!F8</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Unit Mix Summary'!$B$9:$B$18</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Unit Mix Summary'!$F$9:$F$18</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <tx>
-            <strRef>
               <f>'Unit Mix Summary'!H8</f>
             </strRef>
           </tx>
@@ -410,6 +386,30 @@
           <val>
             <numRef>
               <f>'Unit Mix Summary'!$H$9:$H$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Unit Mix Summary'!J8</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Unit Mix Summary'!$B$9:$B$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Unit Mix Summary'!$J$9:$J$18</f>
             </numRef>
           </val>
         </ser>
@@ -468,7 +468,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>10</col>
+      <col>12</col>
       <colOff>0</colOff>
       <row>8</row>
       <rowOff>0</rowOff>
@@ -490,7 +490,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>10</col>
+      <col>12</col>
       <colOff>0</colOff>
       <row>24</row>
       <rowOff>0</rowOff>
@@ -15421,7 +15421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -15430,9 +15430,11 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15527,20 +15529,30 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>NEW LEASE rent</t>
+          <t>LEASES SIGNED rent</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>New #</t>
+          <t>Signed #</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
+          <t>NEW MOVE-IN rent</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Move-In #</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
           <t>Market rent for model</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>Basis</t>
         </is>
@@ -15568,17 +15580,23 @@
         <v/>
       </c>
       <c r="F9" s="7" t="n">
-        <v>1225.222222222222</v>
+        <v>1315.763157894737</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>1225.222222222222</v>
       </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>New leases (n=27)</t>
+      <c r="I9" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="J9" s="7" t="n">
+        <v>1225.222222222222</v>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>New move-ins (n=27)</t>
         </is>
       </c>
     </row>
@@ -15604,17 +15622,23 @@
         <v/>
       </c>
       <c r="F10" s="7" t="n">
-        <v>1167.961538461539</v>
+        <v>1295.333333333333</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="H10" s="7" t="n">
         <v>1167.961538461539</v>
       </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>New leases (n=26)</t>
+      <c r="I10" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="J10" s="7" t="n">
+        <v>1167.961538461539</v>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>New move-ins (n=26)</t>
         </is>
       </c>
     </row>
@@ -15640,17 +15664,23 @@
         <v/>
       </c>
       <c r="F11" s="7" t="n">
-        <v>1355.214285714286</v>
+        <v>1494.53125</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>1355.214285714286</v>
       </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>New leases (n=14)</t>
+      <c r="I11" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="J11" s="7" t="n">
+        <v>1355.214285714286</v>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>New move-ins (n=14)</t>
         </is>
       </c>
     </row>
@@ -15676,17 +15706,23 @@
         <v/>
       </c>
       <c r="F12" s="7" t="n">
-        <v>1322.75</v>
+        <v>1390.833333333333</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H12" s="7" t="n">
         <v>1322.75</v>
       </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>New leases (n=12)</t>
+      <c r="I12" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="J12" s="7" t="n">
+        <v>1322.75</v>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>New move-ins (n=12)</t>
         </is>
       </c>
     </row>
@@ -15712,17 +15748,23 @@
         <v/>
       </c>
       <c r="F13" s="7" t="n">
-        <v>1533.307692307692</v>
+        <v>1652.377777777778</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="H13" s="7" t="n">
         <v>1533.307692307692</v>
       </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>New leases (n=13)</t>
+      <c r="I13" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="J13" s="7" t="n">
+        <v>1533.307692307692</v>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>New move-ins (n=13)</t>
         </is>
       </c>
     </row>
@@ -15748,17 +15790,23 @@
         <v/>
       </c>
       <c r="F14" s="7" t="n">
-        <v>1422.4</v>
+        <v>1565.735294117647</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="H14" s="7" t="n">
         <v>1422.4</v>
       </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>New leases (n=15)</t>
+      <c r="I14" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="J14" s="7" t="n">
+        <v>1422.4</v>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>New move-ins (n=15)</t>
         </is>
       </c>
     </row>
@@ -15784,17 +15832,23 @@
         <v/>
       </c>
       <c r="F15" s="7" t="n">
-        <v>1687</v>
+        <v>1760.6</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H15" s="7" t="n">
         <v>1687</v>
       </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>New leases (n=3)</t>
+      <c r="I15" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" s="7" t="n">
+        <v>1687</v>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>New move-ins (n=3)</t>
         </is>
       </c>
     </row>
@@ -15820,17 +15874,23 @@
         <v/>
       </c>
       <c r="F16" s="7" t="n">
-        <v>1853.25</v>
+        <v>1915.714285714286</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H16" s="7" t="n">
         <v>1853.25</v>
       </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>New leases (n=4)</t>
+      <c r="I16" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="J16" s="7" t="n">
+        <v>1853.25</v>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>New move-ins (n=4)</t>
         </is>
       </c>
     </row>
@@ -15856,17 +15916,23 @@
         <v/>
       </c>
       <c r="F17" s="7" t="n">
-        <v>1948</v>
+        <v>2103</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" s="7" t="n">
         <v>1948</v>
       </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>New leases (n=1)</t>
+      <c r="I17" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="7" t="n">
+        <v>1948</v>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>New move-ins (n=1)</t>
         </is>
       </c>
     </row>
@@ -15891,16 +15957,22 @@
         <f>IFERROR(AVERAGEIFS('Rent Roll'!$J$6:$J$339,'Rent Roll'!$B$6:$B$339,$B18,'Rent Roll'!$F$6:$F$339,"Occupied"),"")</f>
         <v/>
       </c>
-      <c r="F18" s="10" t="n"/>
+      <c r="F18" s="7" t="n">
+        <v>2288</v>
+      </c>
       <c r="G18" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" s="10" t="n"/>
+      <c r="I18" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="7" t="n">
+      <c r="J18" s="7" t="n">
         <v>2288</v>
       </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>In-place — no new leases in window</t>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>In-place — no new move-ins in window</t>
         </is>
       </c>
     </row>
@@ -15923,16 +15995,27 @@
         <f>IFERROR(AVERAGEIFS('Rent Roll'!$J$6:$J$339,'Rent Roll'!$F$6:$F$339,"Occupied"),"")</f>
         <v/>
       </c>
-      <c r="F20" s="14" t="n"/>
+      <c r="F20" s="16">
+        <f>IFERROR(SUMPRODUCT($F$9:$F$18,$G$9:$G$18)/SUM($G$9:$G$18),"")</f>
+        <v/>
+      </c>
       <c r="G20" s="16">
         <f>SUM(G9:G18)</f>
         <v/>
       </c>
       <c r="H20" s="16">
-        <f>IFERROR(SUMPRODUCT($D$9:$D$18,$H$9:$H$18)/SUM($D$9:$D$18),"")</f>
-        <v/>
-      </c>
-      <c r="I20" s="15" t="inlineStr">
+        <f>IFERROR(SUMPRODUCT($H$9:$H$18,$I$9:$I$18)/SUM($I$9:$I$18),"")</f>
+        <v/>
+      </c>
+      <c r="I20" s="16">
+        <f>SUM(I9:I18)</f>
+        <v/>
+      </c>
+      <c r="J20" s="16">
+        <f>IFERROR(SUMPRODUCT($D$9:$D$18,$J$9:$J$18)/SUM($D$9:$D$18),"")</f>
+        <v/>
+      </c>
+      <c r="K20" s="15" t="inlineStr">
         <is>
           <t>Weighted by unit count.</t>
         </is>
@@ -16100,14 +16183,14 @@
     <row r="39" ht="46" customHeight="1">
       <c r="A39" s="20" t="inlineStr">
         <is>
-          <t>Market rent for model is the new-lease average where the plan has new leases inside the lookback window, and the in-place average otherwise — the Basis column says which, per plan. No column on this tab blends lease types, and none of them claims a renewal rent: a roll cannot measure one. A blended "recently leased" average is a renewal average wearing a market-rent label, and on a stabilised property renewals outnumber new leases roughly three to two over twelve months.</t>
+          <t>Market rent for model is the NEW MOVE-IN rent — residents whose move-in date falls inside the lookback window, whatever their lease type — where the plan has one, and the in-place average otherwise; the Basis column says which, per plan; a roll with no usable lease start or move-in date reads in-place outright. LEASES SIGNED is every classified lease started in the window, new and renewal together, and is shown for context only: a blend of new and renewal rents is a renewal average wearing a market-rent label, and on a stabilised property renewals outnumber new leases roughly three to two over twelve months.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="32" customHeight="1">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>New-lease rent, its count and market rent for model are values rather than formulas on purpose: they depend on the window above, and a formula would re-window itself the day this file is reopened. Unit count, average SF and in-place rent are live formulas over the Rent Roll tab.</t>
+          <t>The signed and move-in rents, their counts and market rent for model are values rather than formulas on purpose: they depend on the window above, and a formula would re-window itself the day this file is reopened. Unit count, average SF and in-place rent are live formulas over the Rent Roll tab.</t>
         </is>
       </c>
     </row>
